--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202607/Currency_P&L_20260730.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCurrency/2026/202607/Currency_P&L_20260730.xlsx
@@ -1693,7 +1693,7 @@
         <v>46233</v>
       </c>
       <c r="B41">
-        <v>85859219.67</v>
+        <v>87859219.67</v>
       </c>
       <c r="C41">
         <v>30846.08</v>
